--- a/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_09_Full_107_Cau/Day_09_Ngan_Hang_Phan_01_22_Cau.xlsx
+++ b/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_09_Full_107_Cau/Day_09_Ngan_Hang_Phan_01_22_Cau.xlsx
@@ -673,10 +673,27 @@
       <c r="K4" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Mỗi thay đổi phải trả lời nó sửa symptom nào.
-Phân tích theo nguyên lý thiết kế: Mỗi thay đổi phải trả lời nó sửa symptom nào.</t>
+- [Chẩn đoán đủ 3 triệu chứng quá tải] (1.5 điểm): Chỉ ra lỗi tự phê duyệt hành động tài chính, lỗi nghẽn độ trễ đọc tuần tự, và lỗi trace thiếu tính quan sát.
+- [Thiết kế tách trách nhiệm có căn cứ] (1.5 điểm): Đưa ra các worker chuyên biệt: PolicyWorker (song song), CommunicationWorker, ApprovalGate, PaymentWorker.
+- [Khả năng quan sát và phân quyền bảo mật] (1.0 điểm): Nhấn mạnh ranh giới tách biệt phê duyệt - thực thi và ghi log chuyển trạng thái minh bạch.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Chẩn đoán các triệu chứng quá tải có bằng chứng (Overload Symptoms with Trace Evidence):
+- **Triệu chứng 1: Ô nhiễm ranh giới trách nhiệm và rủi ro quyền hạn (Role Contamination &amp; Security Boundary Overreach)**:
+  Bằng chứng: Một agent duy nhất vừa đọc chính sách, vừa gọi API thanh toán (Payment API có tác động tài chính), vừa viết email và tự xác nhận thao tác của chính mình (Self-Approving Execution). Việc không có cơ chế tách biệt quyền lực (Separation of Concerns / Dual-Control) vi phạm nghiêm trọng nguyên tắc kiểm soát nội bộ.
+- **Triệu chứng 2: Nghẽn cổ chai độ trễ do thực thi tuần tự (Latency Bottleneck via Serial Execution)**:
+  Bằng chứng: Hai nguồn policy độc lập bị đọc nối tiếp (Sequential Reading) thay vì song song hóa (Parallelization), làm tăng gấp đôi độ trễ I/O.
+- **Triệu chứng 3: Thiếu khả năng quan sát và kiểm toán trung gian (Observability Deficit)**:
+  Bằng chứng: Trace chỉ ghi nhận kết quả cuối cùng (`final answer`), che giấu toàn bộ các bước tra cứu, tham số gọi API thanh toán và nội dung email, khiến không thể gỡ lỗi khi thanh toán sai.
+2. Thiết kế tách biệt trách nhiệm xử lý trực tiếp từng triệu chứng:
+- **PolicyRetrievalWorker**: Đọc song song hai nguồn policy độc lập (xử lý Triệu chứng 2).
+- **CustomerCommunicationWorker**: Chuyên trách soạn thảo nội dung email phản hồi.
+- **FinancialApprovalGate / Human-in-the-Loop**: Kiểm tra tính hợp lệ của bằng chứng trước khi chuyển giao lệnh cho PaymentToolWorker.
+- **PaymentToolWorker**: Nhận lệnh đã được phê duyệt để thực hiện giao dịch thanh toán (xử lý Triệu chứng 1).
+- **Orchestration Trace Logger**: Ghi vết chuyển trạng thái (State Transition Traces) qua từng worker (xử lý Triệu chứng 3).
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Một tác tử đơn lẻ gánh vác quá nhiều chức năng (God-Agent Anti-Pattern) vừa gây tắc nghẽn hiệu năng vừa vi phạm bảo mật khi tự phê duyệt các tác vụ có tác dụng phụ (Side-effects). Phân rã thành các tác tử chuyên biệt (Specialized Workers) có ranh giới thẩm quyền và khả năng quan sát từng bước là nguyên lý nền tảng của hệ thống Multi-Agent.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+LangGraph Documentation: 'Multi-Agent Architectures and Separation of Concerns' &amp; Google SRE Principles</t>
         </is>
       </c>
     </row>
@@ -755,10 +772,27 @@
       <c r="K6" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Nêu cả lý do dùng và điều kiện để kết luận nó không đáng.
-Phân tích theo nguyên lý thiết kế: Nêu cả lý do dùng và điều kiện để kết luận nó không đáng.</t>
+- [Quyết định chọn Multi-Agent có căn cứ] (1.0 điểm): Quyết định áp dụng dựa trên 3 kho độc lập, khác biệt chủ quản và yêu cầu cô lập lỗi.
+- [Biện minh lợi ích giảm trễ từ 27s xuống ~11s] (1.5 điểm): Chứng minh việc chạy song song 3 kho 8s giúp giảm trễ hơn một nửa và cô lập lỗi tool.
+- [Phân tích chi phí và Guardrails] (1.0 điểm): Nêu chi phí token điều phối và thiết lập guardrail schema/timeout.
+- [Phép đo và điều kiện thoái lui] (0.5 điểm): Đưa ra metric p95 và điều kiện đảo ngược quyết định nếu không đạt hiệu quả cam kết.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Quyết định: **ĐỒNG Ý CHUYỂN ĐỔI SANG MULTI-AGENT (ADOPT MULTI-AGENT ARCHITECTURE)**:
+Căn cứ: Mặc dù hệ thống đa tác tử có chi phí phức tạp hơn, nhưng kịch bản này hội tụ đủ 3 điều kiện tiên quyết mà một kiến trúc Single-Agent không thể đáp ứng được.
+2. Biện minh chi tiết bằng Lợi ích, Chi phí và Hàng rào bảo vệ (Trade-off Justification):
+- **Lợi ích kỹ thuật (Performance &amp; Isolation Benefits)**:
+  + Tối ưu hóa độ trễ nhảy vọt: Ba kho dữ liệu độc lập (mỗi kho 8s) hiện chạy nối tiếp mất 24s. Khi tách thành 3 Worker chạy song song (Parallel Fan-out), thời gian truy xuất chỉ còn `max(8s, 8s, 8s) = 8s`, giúp hạ độ trễ p95 từ 27s xuống khoảng 11-12s (giảm hơn 55% thời gian phản hồi!).
+  + Cô lập lỗi (Fault Isolation): Lỗi ở Transaction Tool không làm chết toàn bộ tiến trình hay làm mất các bằng chứng thu được từ 3 kho retrieval.
+  + Phân định quyền sở hữu rõ ràng: Policy/Legal Worker và Transaction Worker thuộc hai nhóm chủ quản khác nhau, cho phép phát triển, kiểm thử và phân quyền API độc lập.
+- **Chi phí phát sinh (Overhead Costs)**: Chi phí token tăng nhẹ do trao đổi trạng thái có cấu trúc và chi phí vận hành điều phối (Orchestration Engine overhead).
+- **Hàng rào bảo vệ (Guardrails)**: Cổng kiểm tra hợp đồng dữ liệu (Schema Validation Gate) giữa các worker và cơ chế timeout độc lập 10s cho mỗi kho.
+3. Phép đo sau thay đổi và Điều kiện kết luận nó không đáng (Reversal Condition):
+- Phép đo xác minh: Đo độ trễ `p95 &lt;= 13s` và Tỷ lệ hoàn thành tác vụ khi tool lỗi.
+- **Điều kiện kết luận nó không đáng**: Nếu sau khi triển khai, chi phí token/độ trễ điều phối tăng gấp đôi mà không giảm được p95 xuống dưới 18s do các kho dữ liệu bị nghẽn mạng chung.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Multi-Agent không phải là trào lưu kiến trúc để áp dụng tùy tiện; nó chỉ thực sự đáng giá khi giải quyết được sự cô lập lỗi giữa các chủ thể (Owners) khác nhau và song song hóa được các tác vụ I/O dài (I/O-bound Parallelization). Phân tích đánh đổi định lượng là phẩm chất cốt lõi của kỹ sư phần mềm.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Wu et al. (2023): 'AutoGen: Enabling Next-Gen LLM Applications via Multi-Agent Conversation' &amp; LangGraph Multi-Agent Tradeoffs</t>
         </is>
       </c>
     </row>
@@ -843,10 +877,30 @@
       <c r="K8" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Tìm điểm đổi owner, quyền, dữ liệu hoặc tiêu chí success.
-Phân tích theo nguyên lý thiết kế: Tìm điểm đổi owner, quyền, dữ liệu hoặc tiêu chí success.</t>
+- [Chẩn đoán lỗi mất dấu nguồn gốc ở WorkerA] (1.0 điểm): Chỉ ra WorkerA gộp cả policy và CRM khiến không thể truy vết lỗi do đâu.
+- [Tách biệt 4 Worker có Domain Ownership rõ] (2.0 điểm): Định nghĩa rõ: PolicyWorker (tri thức), CustomerDataWorker (CRM), EligibilityWorker (logic), CommunicationWorker (soạn thảo).
+- [Xác định ranh giới kiểm thử độc lập] (1.0 điểm): Nêu rõ cách viết test boundary riêng biệt cho từng worker (Retrieval benchmark, API mock, Decision table).
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Phân tích nguyên nhân lỗi thiết kế hiện tại:
+WorkerA đang gánh đồng thời hai trách nhiệm thuộc hai miền hoàn toàn khác biệt: đọc chính sách (Policy Knowledge) và đọc hồ sơ khách hàng (CRM Data), rồi tự phán quyết điều kiện đủ (Eligibility). Khi kết quả phán quyết sai, hệ thống gặp hiện tượng **Mất dấu nguồn lỗi (Ambiguous Attribution Defect)**: không thể biết sai do tài liệu chính sách trích xuất sai, do dữ liệu CRM bị lỗi thời, hay do quy tắc suy luận điều kiện bị sai.
+2. Thiết kế lại Bản đồ tác vụ thành các Trách nhiệm Độc lập (Redesigned Task Map):
+- **1. PolicyRetrievalWorker (Domain: Legal/Policy Tri thức)**:
+  + Trách nhiệm duy nhất: Nhận câu hỏi, tìm kiếm và trích xuất đúng các điều khoản chính sách có liên quan.
+  + Đầu ra: `policy_rules: List[RuleChunk]` kèm `policy_version` và citations.
+  + Test boundary: Kiểm thử độc lập bằng bộ testset retrieval (Recall@K, Grounding).
+- **2. CustomerDataWorker (Domain: CRM/Dữ liệu giao dịch)**:
+  + Trách nhiệm duy nhất: Gọi API CRM tra cứu lịch sử mua hàng và thông tin khách hàng.
+  + Đầu ra: `customer_profile: CustomerRecord` có cấu trúc chuẩn hóa.
+  + Test boundary: Kiểm thử hợp đồng API (Mock CRM responses).
+- **3. EligibilityDecisionWorker (Domain: Business Logic Suy luận)**:
+  + Trách nhiệm: Nhận `policy_rules` và `customer_profile` để đối chiếu và đưa ra phán quyết điều kiện đủ.
+  + Đầu ra: `{"is_eligible": bool, "reason": str, "matched_rule_id": str}`.
+  + Test boundary: Kiểm thử bảng quyết định (Unit tests với ma trận điều kiện biên).
+- **4. CommunicationWorker**: Chịu trách nhiệm định dạng JSON và soạn email phản hồi.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Nguyên tắc Trách nhiệm Đơn lẻ (Single Responsibility Principle) trong Multi-Agent: Mỗi tác tử phải có một miền sở hữu (Domain Ownership) và ranh giới kiểm thử (Test Boundary) độc lập. Tách rời tầng thu thập dữ liệu (Policy, CRM) khỏi tầng ra quyết định (Decision Engine) giúp định vị chính xác nguồn gốc lỗi khi phát sinh sự cố.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+CrewAI Documentation: 'Role-Playing and Task Decomposition' &amp; Martin Fowler: 'Single Responsibility Principle in Distributed Systems'</t>
         </is>
       </c>
     </row>
@@ -925,10 +979,40 @@
       <c r="K10" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Tìm fan-out, fan-in và điểm commit consequence.
-Phân tích theo nguyên lý thiết kế: Tìm fan-out, fan-in và điểm commit consequence.</t>
+- [Vẽ đúng cấu trúc đồ thị DAG] (1.5 điểm): Thể hiện rõ fan-out song song fetch_hr/fetch_legal, fan-in tại merge, đi qua approve rồi tới write_case tuần tự.
+- [Xác định điểm cam kết kết quả write_case] (1.0 điểm): Nhận diện write_case là side-effect commit point đòi hỏi kiểm soát nghiêm ngặt.
+- [Bất biến Idempotency &amp; State Lock chống ghi 2 lần] (1.5 điểm): Thiết lập cờ trạng thái case_written, mutex lock và mã Idempotency Key gửi kèm lệnh ghi.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Vẽ Sơ đồ Phụ thuộc và Lịch chạy (Dependency &amp; Execution Graph):
+Sơ đồ luồng đồ thị DAG (Directed Acyclic Graph) phân tách rõ ràng giữa đọc song song và ghi tuần tự:
+```text
+       [START]
+       /     \
+  (Fan-out: Đọc song song)
+     /         \
+ [fetch_hr]   [fetch_legal]
+     \         /
+  (Fan-in: Hợp nhất bằng chứng)
+       \     /
+       [merge]
+          |
+          v
+      [approve]  (Xác nhận điều kiện / Human Gate)
+          |
+          v
+    [write_case] (Tuần tự hóa - Điểm cam kết kết quả có tác dụng phụ)
+          |
+        [END]
+```
+2. Bất biến ngăn chặn ghi hai lần (Double-Write Prevention Invariant):
+- **Bất biến Khóa Trạng thái và Khóa Lũy thừa (Idempotency Key &amp; State Lock Invariant)**:
+  `write_case` là thao tác có tác dụng phụ (Side-effect Commit Point). Để đảm bảo không bao giờ chạy 2 lần, hệ thống áp dụng 2 cơ chế kiểm soát:
+  (a) **Khóa chuyển trạng thái nghiêm ngặt (Strict State Transition)**: Node `write_case` chỉ được phép kích hoạt khi `state.status == 'approved'` VÀ `state.case_written == False`. Khi bắt đầu chạy, nó lập tức cập nhật trạng thái tạm thời thành `writing` (hoặc giữ Distributed Mutex Lock trên `case_id`).
+  (b) **Mã khóa Idempotency Key (Idempotent API Call)**: Lệnh ghi vào cơ sở dữ liệu được gửi kèm `idempotency_key = hash(case_id + approval_timestamp)`. Nếu node bị kích hoạt lại ngẫu nhiên, hệ thống cơ sở dữ liệu backend sẽ từ chối thao tác ghi trùng lặp và trả về kết quả đã ghi trước đó.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Mẫu kiến trúc Parallel-Read Serialized-Write (Đọc song song - Ghi tuần tự) là khuôn mẫu kinh điển trong các hệ thống giao dịch. Các tác vụ thu thập thông tin được tối ưu hóa tốc độ bằng cơ chế Fan-out song song, nhưng bước phát sinh tác dụng phụ (Commit) bắt buộc phải qua rào cản đồng bộ hóa (Barrier/Fan-in) và bảo vệ bằng Idempotency Key để chống Double-Spending / Double-Write.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+LangGraph Documentation: 'Graph Branching, Merging &amp; State Reducers' &amp; Designing Data-Intensive Applications (Kleppmann)</t>
         </is>
       </c>
     </row>
@@ -1052,10 +1136,27 @@
       <c r="K13" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Tìm cluster có policy/ownership chung và kiểm chi phí của một hop mới.
-Phân tích theo nguyên lý thiết kế: Tìm cluster có policy/ownership chung và kiểm chi phí của một hop mới.</t>
+- [Quyết định thêm Hierarchy có căn cứ] (1.5 điểm): Khẳng định nên thêm phân cấp vì 14 workers làm quá tải prompt và tăng misroute; nhận diện cụm 6 Finance workers có shared policy.
+- [Thiết kế cấu trúc 2 tầng tối thiểu] (1.5 điểm): Mô tả rõ Root Supervisor quản lý 8 workers + FinanceSupervisor; FinanceSupervisor quản lý 6 Finance workers.
+- [Chỉ số xác minh thực nghiệm] (1.0 điểm): Đưa ra 3 metric cụ thể: Misroute rate giảm, token prompt giảm 35%, Task success rate tăng.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Có nên thêm tầng phân cấp (Hierarchy) không?
+**CÓ, HOÀN TOÀN NÊN THÊM.**
+Căn cứ: Một Supervisor duy nhất điều phối trực tiếp (flat routing) 14 workers độc lập đã vượt quá dung lượng ngữ cảnh hiệu quả (Context Overload) của mô hình định tuyến. Danh sách worker dài làm tăng token prompt, gây nhầm lẫn ngữ nghĩa giữa các năng lực và là nguyên nhân trực tiếp khiến tỷ lệ định tuyến sai (misroute rate) tăng vọt. Sự hiện diện của cụm 6 workers Finance có chính sách dùng chung là tín hiệu hoàn hảo để trừu tượng hóa phân cấp.
+2. Đề xuất cấu trúc phân cấp tối thiểu (Minimal Hierarchical Structure):
+Thiết lập cấu trúc 2 tầng (Two-Tier Hierarchical Multi-Agent Architecture):
+- **Tầng 1 (Top-level Root Supervisor)**: Chỉ quản lý **9 thực thể** (thay vì 14):
+  + 8 General/Domain Workers độc lập.
+  + 1 Sub-Supervisor: `FinanceSupervisor` (đại diện cho toàn bộ miền tài chính).
+- **Tầng 2 (Finance Subgraph)**: Được điều phối bởi `FinanceSupervisor`, quản lý nội bộ 6 Finance Workers với chính sách dùng chung.
+3. Hệ thống chỉ số xác minh hiệu quả (Verification Metrics):
+- **Top-level Misroute Rate**: Tỷ lệ định tuyến sai của Root Supervisor giảm xuống mức tối thiểu (mục tiêu &lt; 2%).
+- **Prompt Token Reduction**: Dung lượng token danh sách worker trong system prompt của Root Supervisor giảm ít nhất 35%.
+- **End-to-End Task Success Rate**: Tỷ lệ hoàn thành tác vụ chính xác toàn trình tăng đáng kể trên toàn bộ 14 nghiệp vụ.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Quy tắc Sizing trong hệ thống tác tử: Khi số lượng worker vượt quá ngưỡng 7-10 tác tử, mô hình ngôn ngữ làm nhiệm vụ điều phối bắt đầu bị suy giảm độ chính xác định tuyến. Gom cụm các tác tử có chung miền chính sách và trách nhiệm vào một Subgraph có Sub-Supervisor riêng giúp giảm tải nhận thức (Cognitive Load) cho Root Supervisor và tăng tính module hóa của hệ thống.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Wu et al. (2023): 'AutoGen: Hierarchical Multi-Agent Group Chat' &amp; LangGraph Subgraph Composition</t>
         </is>
       </c>
     </row>
@@ -1134,10 +1235,31 @@
       <c r="K15" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Supervisor giữ flow; worker giữ domain skill.
-Phân tích theo nguyên lý thiết kế: Supervisor giữ flow; worker giữ domain skill.</t>
+- [Chỉ rõ 2 lỗi vi phạm ranh giới] (1.5 điểm): Nhận diện đúng lỗi Supervisor tự trả lời (vi phạm vai trò điều phối) và lỗi coi RetrievalWorker là bãi rác catch-all.
+- [Nguyên tắc kiến trúc Supervisor-Worker] (1.0 điểm): Nhấn mạnh nguyên tắc: Supervisor giữ flow điều phối, Worker giữ domain skill.
+- [Viết lại Routing Contract chuẩn xác] (1.5 điểm): Thiết kế JSON schema định tuyến tường minh (next_worker, routing_reason) cấm supervisor tự sinh text trả lời.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Chỉ ra hai lỗi vi phạm ranh giới trách nhiệm (Boundary Violations):
+- **Lỗi 1: Supervisor kiêm nhiệm xử lý nghiệp vụ (Domain Logic Contamination)**:
+  Supervisor hiện 'tự trả lời policy' khi cảm thấy tự tin. Đây là lỗi vi phạm nghiêm trọng ranh giới: Supervisor chỉ có vai trò điều phối luồng (Flow Orchestration), tuyệt đối không được kiêm nhiệm vai trò tri thức miền (Domain Worker). Khi tự trả lời, supervisor dễ sinh ra ảo giác và bỏ qua các quy tắc trích dẫn chuẩn.
+- **Lỗi 2: Thiếu bộ định tuyến chuyên biệt &amp; Đổ dồn yêu cầu (Default Dump / Catch-all Routing Defect)**:
+  Supervisor 'chỉ gọi worker khi thiếu tự tin và đẩy mọi request còn lại vào RetrievalWorker'. Việc coi RetrievalWorker là thùng chứa rác (catch-all) làm mất vai trò của các worker khác (nếu có) và biến hệ thống thành một luồng tùy tiện không thể kiểm soát.
+2. Viết lại Hợp đồng Định tuyến (Rewritten Routing Contract):
+Nguyên tắc cốt lõi: 'Supervisor giữ luồng điều phối; Worker giữ tri thức và năng lực miền'.
+Hợp đồng bắt buộc Supervisor chỉ xuất ra cấu trúc JSON định tuyến, cấm tự viết câu trả lời trực tiếp:
+```json
+{
+  "next_worker": "PolicyWorker" | "RetrievalWorker" | "SynthesisWorker" | "FINISH",
+  "routing_reason": "string giải thích căn cứ điều phối",
+  "delegation_payload": {"sub_task": "string", "context_keys": ["..."]}
+}
+```
+- Nếu yêu cầu là câu hỏi chính sách: Bắt buộc định tuyến sang `PolicyWorker` (hoặc `RetrievalWorker`).
+- Khi tất cả các worker đã hoàn tất dữ liệu: Định tuyến sang `SynthesisWorker` để tổng hợp phản hồi cuối cùng.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Mẫu thiết kế Supervisor-Worker đòi hỏi sự phân định nghiêm ngặt: Supervisor là trọng tài điều phối luồng, không được tự ý ra sân thi đấu thay cho cầu thủ (Workers). Việc Supervisor tự trả lời là biểu hiện của sự lỏng lẻo trong prompt contract, làm mất tính tất định và phá hủy khả năng kiểm thử của từng tác tử.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+LangChain Documentation: 'Supervisor Multi-Agent Pattern' &amp; AutoGen GroupChatManager Architecture</t>
         </is>
       </c>
     </row>
@@ -1220,10 +1342,23 @@
       <c r="K17" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Nếu route không thay đổi theo input thì router đang quyết định điều gì?
-Phân tích theo nguyên lý thiết kế: Nếu route không thay đổi theo input thì router đang quyết định điều gì?</t>
+- [Lựa chọn Sequential Pipeline &amp; Bác bỏ Dynamic Router] (1.5 điểm): Chọn Pipeline tất định; giải thích Router không có gì để quyết định vì luồng cố định, chỉ gây tốn trễ và rủi ro misroute.
+- [Thiết lập Checkpoints rõ ràng sau từng bước] (1.5 điểm): Đặt checkpoint sau Parse và sau Validate để lưu trạng thái trung gian phục vụ phục hồi.
+- [Hành vi xử lý lỗi và bảo vệ bước Publish] (1.0 điểm): Dừng sớm nếu parse/validate lỗi, chỉ publish khi pass validation kèm cơ chế retry.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Lựa chọn Mẫu Thiết kế (Pattern Selection):
+Chọn **Deterministic Sequential Pipeline (Đường ống Tuần tự Tất định)**. Tuyệt đối **KHÔNG CẦN VÀ KHÔNG NÊN DÙNG DYNAMIC SUPERVISOR ROUTER**.
+2. Biện minh vì sao Dynamic Router hoàn toàn không cần thiết:
+- Bản chất luồng công việc: Quy trình `parse -&gt; validate -&gt; publish` luôn luôn thực thi theo cùng một thứ tự tuyến tính cố định cho mọi đầu vào. Ranh giới giữa các bước là bất biến.
+- Router chỉ có giá trị khi cần rẽ nhánh động (Branching) dựa trên nội dung câu hỏi hoặc phân loại trạng thái. Trong một quy trình tuyến tính cố định, một Dynamic Router LLM không có bất kỳ quyết định nào để đưa ra; việc đưa nó vào chỉ làm lãng phí token, tăng thêm 500-1000 ms độ trễ cho mỗi bước và tạo ra nguy cơ mô hình định tuyến nhầm sang một thứ tự vô lý (ví dụ: nhảy từ `parse` sang thẳng `publish`).
+3. Thiết lập Điểm lưu Checkpoint và Hành vi khi có Lỗi (Checkpoint &amp; Error Behavior):
+- **Checkpoint 1 (Sau Parse)**: Lưu `state.parsed_artifact`. Nếu Parse thất bại -&gt; Lập tức kết thúc với `status = 'failed_parse'`, không gọi tiếp.
+- **Checkpoint 2 (Sau Validate)**: Lưu `state.validation_result`. Nếu Validation không hợp lệ -&gt; Kết thúc với `status = 'failed_validation'`, kích hoạt thông báo cho người dùng.
+- **Điểm cam kết Publish (Side-effect Gate)**: Chỉ kích hoạt `publish` khi và chỉ khi `state.validation_passed == True`. Áp dụng cơ chế giao dịch (Transactional Commit) để nếu publish lỗi mạng, hệ thống có thể thử lại an toàn dựa trên checkpoint của Validate mà không cần parse lại từ đầu.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Quy tắc Kỹ thuật: 'Đừng dùng tác tử thông minh LLM để giải quyết bài toán mà một đoạn code tuần tự đơn giản có thể làm tốt hơn'. Pipeline tuần tự tất định với các điểm lưu Checkpoint rõ ràng mang lại tính tin cậy 100%, độ trễ tối thiểu và khả năng phục hồi lỗi hoàn hảo.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+LangGraph Documentation: 'Sequential Workflows vs. Multi-Agent Graphs' &amp; Fowler: 'Pipes and Filters Architecture'</t>
         </is>
       </c>
     </row>
@@ -1302,10 +1437,26 @@
       <c r="K19" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Một phiếu không mạnh hơn chỉ vì nó được sinh hai lần.
-Phân tích theo nguyên lý thiết kế: Một phiếu không mạnh hơn chỉ vì nó được sinh hai lần.</t>
+- [Phê phán cơ chế Majority Vote] (1.5 điểm): Chỉ ra việc 2 agent cùng prompt sinh đồng thuận ảo đè bẹp agent thứ 3 có nguồn chính sách thẩm quyền.
+- [Quy tắc Judging dựa trên thang bậc bằng chứng] (1.5 điểm): Thiết kế thẩm phán đánh giá dựa trên nguồn trích dẫn được xác thực và vòng đối chất phản biện.
+- [Điều kiện dừng hữu hạn] (1.0 điểm): Giới hạn tối đa 2 vòng debate và cơ chế fallback chuyển cấp con người nếu bất đồng kéo dài.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Phân tích sai lầm của cơ chế Đa số Thắng (Majority Voting Flaw):
+Nguyên tắc: 'Một ý kiến sai lặp lại hai lần không trở thành chân lý' (Duplicate Hallucination Trap). Hai agent cùng dùng chung một prompt/mô hình đã sinh ra hai câu trả lời đồng thuận ảo do cùng chia sẻ một thiên kiến (Model Bias). Trong khi đó, Agent thứ ba tuy là thiểu số (1 phiếu) nhưng lại dẫn nguồn tài liệu chính sách có thẩm quyền (Authoritative Citation) và chứng minh được tính đúng đắn. Cơ chế majority vote thuần túy đã đàn áp sự thật và chọn câu trả lời sai.
+2. Thiết kế lại Quy tắc Tranh luận và Đánh giá (Redesigned Debate &amp; Judging Rules):
+- **Thay thế Majority Vote bằng Bằng chứng Trọng tài (Evidence-Based Adjudication)**:
+  Thẩm phán độc lập (Judge / Meta-Agent) đánh giá các câu trả lời dựa trên Thang bậc Bằng chứng (Hierarchy of Evidence):
+  + Trọng số 1 (Thẩm quyền cao nhất): Mệnh đề có trích dẫn văn bản chính sách chính thức được xác thực (Verified Statutory Citation).
+  + Trọng số 2: Lập luận logic không mâu thuẫn.
+  + Không tính điểm số lượng bản sao: Hai câu trả lời giống nhau từ cùng prompt chỉ được tính là một nguồn dữ liệu duy nhất.
+- **Vòng tranh biện đối chất (Cross-Examination Round)**: Thẩm phán gửi trích dẫn của Agent 3 cho Agent 1 và 2: 'Agent 3 dẫn chứng Điều 5 Quy định X trái ngược với câu trả lời của bạn. Bạn có tài liệu chính thức nào phủ nhận Điều 5 không?'. Nếu hai agent không dẫn được nguồn phản bác, Agent 3 thắng cuộc.
+3. Điều kiện dừng hữu hạn (Stopping Conditions):
+- Điều kiện 1: Các bên đạt được sự đồng thuận dựa trên bằng chứng tối thượng.
+- Điều kiện 2: Đạt giới hạn tối đa **2 vòng tranh biện (Max Rounds = 2)**. Nếu vẫn bất đồng, Judge ưu tiên bên có trích dẫn thẩm quyền và đánh dấu cờ kiểm tra cho con người.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Trong hệ thống tác tử tranh luận (Debate Pattern), sự thật khách quan phải được xác định bằng tính vững chắc của bằng chứng (Evidence Grounding), hoàn toàn không thể giải quyết bằng cơ chế bỏ phiếu dân chủ (Majority Voting) giữa các mô hình ngôn ngữ vốn dễ mắc lỗi đồng thuận ảo (Sycophancy).
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Du et al. (2023): 'Improving Factuality and Reasoning in Language Models through Multiagent Debate' &amp; Anthropic Constitutional Principles</t>
         </is>
       </c>
     </row>
@@ -1429,10 +1580,26 @@
       <c r="K22" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Hỏi vấn đề nào đang tồn tại mà một tầng mới sửa được.
-Phân tích theo nguyên lý thiết kế: Hỏi vấn đề nào đang tồn tại mà một tầng mới sửa được.</t>
+- [Đánh giá dư thừa của đề xuất 2 tầng] (1.5 điểm): Bác bỏ đề xuất: 4 worker phẳng đang đạt 99% accuracy; thêm tầng chỉ làm tăng trễ 1-2s và tốn token vô ích.
+- [Tác hại của việc phân cấp sớm] (1.0 điểm): Nêu rõ rủi ro tích lũy lỗi qua nhiều hop (Error Cascading) và chi phí vận hành tăng cao.
+- [3 Tín hiệu kích hoạt phân cấp thực sự] (1.5 điểm): Liệt kê 3 tín hiệu chuẩn xác: số lượng worker &gt; 10 làm giảm accuracy, xuất hiện cụm nghiệp vụ có shared state/policy, và yêu cầu cách ly bảo mật.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Đánh giá đề xuất thêm 2 tầng Supervisor (Evaluation of Over-Engineering):
+Đề xuất này là **MỘT THIẾT KẾ DƯ THỪA TAI HẠI (Premature Optimization &amp; Over-Engineering Anti-pattern)**:
+- Căn cứ thực tế: Hệ thống hiện tại chỉ có 4 workers độc lập và độ chính xác định tuyến (Routing Accuracy) đang đạt mức lý tưởng 99%. Không có bất kỳ vấn đề nào về hiệu năng, độ chính xác hay quá tải prompt xảy ra trong hệ thống.
+- Tác hại của việc thêm 2 tầng Supervisor:
+  + Tăng thêm 2 chặng mạng/LLM (Extra Hops), làm tăng độ trễ p95 thêm ít nhất 1.000 ms đến 2.000 ms cho mỗi yêu cầu.
+  + Làm tăng gấp đôi chi phí token điều phối.
+  + Làm tăng nguy cơ lỗi tích lũy giữa các tầng (Error Cascading) và giảm độ chính xác từ 99% xuống thấp hơn do thêm điểm thất bại tiềm tàng.
+2. Các tín hiệu kỹ thuật (Signals) thực sự làm phân cấp trở nên đáng cân nhắc trong tương lai:
+Chỉ xem xét thêm tầng phân cấp (Hierarchy) khi xuất hiện ít nhất một trong ba tín hiệu sau:
+- **Tín hiệu 1 (Bùng nổ số lượng Worker)**: Số lượng worker mở rộng vượt quá 10-12 workers khiến system prompt của supervisor bị quá tải token và tỷ lệ misroute tăng cao (&gt; 5%).
+- **Tín hiệu 2 (Hình thành các Cụm nghiệp vụ chuyên biệt có ranh giới rõ ràng)**: Xuất hiện các nhóm worker có chung chính sách, chung cơ sở dữ liệu nội bộ và quyền hạn riêng biệt (ví dụ: Cụm Kế toán 5 workers, Cụm Pháp chế 4 workers).
+- **Tín hiệu 3 (Yêu cầu Cô lập Bảo mật / Tenant Boundaries)**: Khi các nhóm worker thuộc các bộ phận khác nhau không được phép chia sẻ chung không gian trạng thái hoặc log truy vết.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Nguyên lý YAGNI (You Aren't Gonna Need It) trong Kiến trúc Multi-Agent: Đừng bao giờ xây dựng hệ thống phân cấp phức tạp cho tương lai 'scale sau này' khi bài toán hiện tại đang hoạt động hoàn hảo với 4 worker phẳng. Thêm tầng điều phối đồng nghĩa với việc thêm độ trễ, chi phí và điểm gãy của hệ thống.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Google SRE Principles: 'Simplicity and Premature Optimization' &amp; Martin Fowler: 'YAGNI (You Aren't Gonna Need It)'</t>
         </is>
       </c>
     </row>
@@ -1512,10 +1679,28 @@
       <c r="K24" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Tách 'node nào tồn tại' khỏi 'node nào được chọn ở run này'.
-Phân tích theo nguyên lý thiết kế: Tách 'node nào tồn tại' khỏi 'node nào được chọn ở run này'.</t>
+- [Phân định phần Tĩnh] (1.5 điểm): Xác định rõ cấu trúc nodes (classify, route, merge), các cạnh cố định và State schema là phần tĩnh compile-time.
+- [Phân định phần Động] (1.0 điểm): Xác định việc chọn worker tại conditional edge dựa trên runtime label là phần động.
+- [Thiết lập 3 Test Invariants bắt buộc] (1.5 điểm): Định nghĩa các invariant: tập nhãn đóng có fallback, mọi đường chạy đều hội tụ về merge, và không tự biến đổi đồ thị runtime.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Phân định thành phần Tĩnh và thành phần Động trong Đồ thị:
+- **Phần Tĩnh (Static Graph Topology / Compile-time Invariants)**:
+  + Tập hợp các Node cố định đã được khai báo và biên dịch trong đồ thị: `{classify, route, worker_pool, merge}`.
+  + Các cạnh kết nối cấu trúc bất biến: `START -&gt; classify -&gt; route` và `worker -&gt; merge -&gt; END`.
+  + Lược đồ trạng thái chung (State Schema Definition) quy định kiểu dữ liệu của các trường trong graph.
+- **Phần Động (Dynamic Execution Routing / Runtime Selection)**:
+  + Quyết định rẽ nhánh tại node `route`: Node `route` đọc nhãn phân loại runtime (ví dụ `label = 'billing'`) để chọn cạnh có điều kiện (Conditional Edge) kích hoạt worker cụ thể (`BillingWorker`).
+  + Dữ liệu payload thực tế được truyền qua các node trong một lần chạy cụ thể.
+2. Các điều kiện kiểm thử bất biến bắt buộc cần có (Test Invariants):
+- **Invariant 1: Tính Đóng kín của Nhãn Điều phối (Finite Closed-set Routing Invariant)**:
+  `assert route_label in ALLOWED_WORKER_LABELS` — Nhãn sinh ra từ node `classify` bắt buộc phải thuộc danh mục các worker tồn tại thực tế trong đồ thị. Nếu nhãn lạ, bắt buộc rẽ về nhánh `fallback_worker`.
+- **Invariant 2: Bảo toàn Dòng chảy Hợp nhất (Merge Convergence Invariant)**:
+  Dù bất kỳ worker động nào được kích hoạt, 100% các nhánh rẽ đều phải hội tụ về node `merge` trước khi kết thúc (không có nhánh cụt treo trạng thái).
+- **Invariant 3: Tính Bất biến Cấu trúc Đồ thị**: Đồ thị không được tự ý sửa đổi danh sách node tại thời điểm chạy (No runtime graph mutation).
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Trong LangGraph và các framework điều phối hiện đại, cấu trúc đồ thị (Nodes &amp; Edges) là cấu trúc tĩnh được kiểm tra chặt chẽ khi khởi tạo (Build-time), trong khi việc chọn đường đi giữa các cạnh có điều kiện là hành vi động (Runtime Decision). Phân định rõ hai yếu tố này giúp thiết lập các kiểm thử bất biến đảm bảo hệ thống không bao giờ bị rơi vào trạng thái treo (Deadlock / Dangling State).
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+LangGraph Documentation: 'Conditional Edges and Static Graph Compilation' (https://langchain-ai.github.io/langgraph/)</t>
         </is>
       </c>
     </row>
